--- a/docs/commercial/tenders/sky-blog-2026/propuesta-economica.xlsx
+++ b/docs/commercial/tenders/sky-blog-2026/propuesta-economica.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>PROPUESTA ECONÓMICA</t>
   </si>
@@ -43,37 +43,40 @@
     <t>120 días desde su recepción por parte de SKY</t>
   </si>
   <si>
-    <t>1. TARIFAS</t>
+    <t>1. VALOR DEL SERVICIO</t>
   </si>
   <si>
     <t>Plan</t>
   </si>
   <si>
-    <t>Alcance mensual</t>
+    <t>Alcance de la operación mensual</t>
   </si>
   <si>
     <t>Valor mensual (CLP, neto sin IVA)</t>
   </si>
   <si>
-    <t>Base (propuesto)</t>
-  </si>
-  <si>
-    <t>8 artículos/mes + SEO/AEO + recursos visuales + reportería</t>
-  </si>
-  <si>
-    <t>Ampliado (opcional)</t>
-  </si>
-  <si>
-    <t>12 artículos/mes + SEO/AEO + recursos visuales + reportería</t>
-  </si>
-  <si>
-    <t>Artículo adicional / ad-hoc</t>
-  </si>
-  <si>
-    <t>Por artículo, sobre el plan contratado</t>
-  </si>
-  <si>
-    <t>Valor del plan base — proyección del contrato</t>
+    <t>Plan propuesto</t>
+  </si>
+  <si>
+    <t>Operación mensual del blog: estrategia y planificación editorial · capa técnica de SEO implementada sobre su WordPress · producción de hasta 8 artículos publicados · recursos visuales y multimedia · medición en buscadores y en los 5 motores de respuesta con IA · informe mensual con los 8 indicadores exigidos · portal de cliente en vivo · gobernanza con los 9 SLA de las Bases</t>
+  </si>
+  <si>
+    <t>Plan ampliado (opcional)</t>
+  </si>
+  <si>
+    <t>La misma operación, con capacidad de producción de hasta 12 artículos publicados al mes</t>
+  </si>
+  <si>
+    <t>Contenidos ad-hoc</t>
+  </si>
+  <si>
+    <t>Se producen DENTRO de la capacidad mensual contratada, con la prioridad que SKY determine y en ≤ 5 días hábiles. Sin costo adicional: un contenido ad-hoc ocupa un espacio de la capacidad del mes.</t>
+  </si>
+  <si>
+    <t>Incluido</t>
+  </si>
+  <si>
+    <t>Proyección del plan propuesto</t>
   </si>
   <si>
     <t>Anual (12 meses)</t>
@@ -85,10 +88,10 @@
     <t>2. CONDICIONES COMERCIALES</t>
   </si>
   <si>
-    <t>Moneda</t>
-  </si>
-  <si>
-    <t>Pesos chilenos (CLP) — proveedor chileno</t>
+    <t>Precio</t>
+  </si>
+  <si>
+    <t>CLP 5.200.000 mensuales, valor neto. Tarifa fija en pesos chilenos, conforme al numeral 3.2 de las Bases</t>
   </si>
   <si>
     <t>Impuestos</t>
@@ -100,43 +103,43 @@
     <t>Reajustes</t>
   </si>
   <si>
-    <t>Sin reajuste durante la vigencia del contrato</t>
+    <t>Sin reajuste durante la vigencia del contrato, conforme al numeral 3.2 de las Bases</t>
+  </si>
+  <si>
+    <t>Condiciones de pago</t>
+  </si>
+  <si>
+    <t>30 días desde la correcta recepción y aceptación conforme de la factura por parte de SKY</t>
+  </si>
+  <si>
+    <t>Facturación</t>
+  </si>
+  <si>
+    <t>Mensual</t>
+  </si>
+  <si>
+    <t>Modalidad de pago</t>
+  </si>
+  <si>
+    <t>Transferencia electrónica a la cuenta bancaria de Efeonce Group SpA</t>
+  </si>
+  <si>
+    <t>Duración</t>
+  </si>
+  <si>
+    <t>Dos (2) años a contar del inicio del servicio</t>
+  </si>
+  <si>
+    <t>Condiciones de término</t>
+  </si>
+  <si>
+    <t>Renovable por igual período previo acuerdo de ambas partes, con notificación 60 días antes del término del período en curso (numeral 3.3.2 de las Bases)</t>
   </si>
   <si>
     <t>Desembolsos</t>
   </si>
   <si>
-    <t>No aplican. El valor mensual es todo incluido (planificación, producción, SEO/AEO, recursos visuales, reportería y coordinación). Sin gastos reembolsables ni costos ocultos</t>
-  </si>
-  <si>
-    <t>Condiciones de pago</t>
-  </si>
-  <si>
-    <t>30 días desde la correcta recepción y aceptación conforme de la factura por parte de SKY</t>
-  </si>
-  <si>
-    <t>Facturación</t>
-  </si>
-  <si>
-    <t>Mensual</t>
-  </si>
-  <si>
-    <t>Modalidad de pago</t>
-  </si>
-  <si>
-    <t>Transferencia electrónica</t>
-  </si>
-  <si>
-    <t>Duración del contrato</t>
-  </si>
-  <si>
-    <t>Dos (2) años a contar del inicio del servicio</t>
-  </si>
-  <si>
-    <t>Condiciones de término</t>
-  </si>
-  <si>
-    <t>Renovable por igual período previo acuerdo de las partes, con aviso de 60 días antes del término</t>
+    <t>No aplican. El valor mensual es todo incluido: planificación, capa técnica, producción, recursos visuales, multimedia, medición, portal y coordinación. Sin gastos reembolsables ni costos ocultos</t>
   </si>
   <si>
     <t>Comisiones de plataforma</t>
@@ -152,7 +155,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="11" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+  </numFmts>
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -162,12 +168,29 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF023C70"/>
-      <sz val="18"/>
+      <color rgb="FF0F2A4A"/>
+      <sz val="16"/>
       <name val="Calibri"/>
     </font>
     <font>
       <color rgb="FF5B6470"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF141821"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF141821"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0F2A4A"/>
       <sz val="12"/>
       <name val="Calibri"/>
     </font>
@@ -184,42 +207,17 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF023C70"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF023C70"/>
+      <color rgb="FF0F2A4A"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
       <color rgb="FF5B6470"/>
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <b/>
-      <color rgb="FF023C70"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF5B6470"/>
-      <sz val="9"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -229,11 +227,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF5F7FA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF023C70"/>
       </patternFill>
     </fill>
   </fills>
@@ -264,7 +257,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -272,38 +265,52 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -644,527 +651,230 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B2:D33"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="46" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="3" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="72" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+    <row r="1" ht="26" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="5" ht="16" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" ht="16" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" ht="16" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" ht="16" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" ht="30" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
+    </row>
+    <row r="10" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="B10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="C10" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
+    <row r="11" ht="76" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="B11" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="9">
+      <c r="C11" s="10">
         <v>5200000</v>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="4" t="s">
+    <row r="12" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="B12" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="10">
+      <c r="C12" s="11">
         <v>6900000</v>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
+    <row r="13" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="B13" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="10">
-        <v>260000</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="11" t="s">
+      <c r="C13" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-    </row>
-    <row r="17" ht="16" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="4" t="s">
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="12">
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="16"/>
+      <c r="C16" s="11">
         <v>62400000</v>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="12">
+    <row r="17" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="17"/>
+      <c r="C17" s="18">
         <v>124800000</v>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="3" t="s">
+    <row r="19" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="4" t="s">
+    </row>
+    <row r="20" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="3" t="s">
+      <c r="B20" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C20" s="16"/>
+    </row>
+    <row r="21" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="4"/>
-    </row>
-    <row r="23" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="3" t="s">
+      <c r="B21" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C21" s="16"/>
+    </row>
+    <row r="22" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24" ht="42" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="s">
+      <c r="B22" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C22" s="16"/>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="4"/>
-    </row>
-    <row r="25" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="3" t="s">
+      <c r="B23" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C23" s="16"/>
+    </row>
+    <row r="24" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="4"/>
-    </row>
-    <row r="26" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="3" t="s">
+      <c r="B24" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C24" s="16"/>
+    </row>
+    <row r="25" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="4"/>
-    </row>
-    <row r="27" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B27" s="3" t="s">
+      <c r="B25" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C25" s="16"/>
+    </row>
+    <row r="26" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B28" s="3" t="s">
+      <c r="B26" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C26" s="16"/>
+    </row>
+    <row r="27" ht="46" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="4"/>
-    </row>
-    <row r="29" ht="42" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B29" s="3" t="s">
+      <c r="B27" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C27" s="16"/>
+    </row>
+    <row r="28" ht="46" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="4"/>
-    </row>
-    <row r="30" ht="42" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" s="3" t="s">
+      <c r="B28" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C28" s="16"/>
+    </row>
+    <row r="29" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D30" s="4"/>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B33" s="13" t="s">
+      <c r="B29" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
+      <c r="C29" s="16"/>
+    </row>
+    <row r="31" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="19" t="s">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="B33:D33"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009D828160AC62D2469F2CE6ED288EED23" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="2cd7cb4357131406ef2560062547c01c">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89d25d81-5310-4cf1-bb5a-6a617d2b6a73" xmlns:ns3="3c9eec10-562a-438c-b6b5-17a823518688" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="93f478c6cac0bb3a9ff43bd8511d61be" ns2:_="" ns3:_="">
-    <xsd:import namespace="89d25d81-5310-4cf1-bb5a-6a617d2b6a73"/>
-    <xsd:import namespace="3c9eec10-562a-438c-b6b5-17a823518688"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:Fecha" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="89d25d81-5310-4cf1-bb5a-6a617d2b6a73" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="9" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="8b9bf029-62f4-4345-b8e5-422487cfd5ed" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="15" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Fecha" ma:index="19" nillable="true" ma:displayName="Fecha" ma:default="[today]" ma:format="DateTime" ma:internalName="Fecha">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:DateTime"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="22" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3c9eec10-562a-438c-b6b5-17a823518688" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="10" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{0ab32602-a2c3-4267-9b10-aa875bd30e36}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3c9eec10-562a-438c-b6b5-17a823518688">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="89d25d81-5310-4cf1-bb5a-6a617d2b6a73">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3c9eec10-562a-438c-b6b5-17a823518688" xsi:nil="true"/>
-    <Fecha xmlns="89d25d81-5310-4cf1-bb5a-6a617d2b6a73">2026-07-12T09:55:42+00:00</Fecha>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0FC00D0-9E4D-4F97-AAFC-33A791EFC979}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4994FC4-F8AC-4A2A-A98A-C829B40B4951}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01CFE923-56D7-42A4-A493-C93B7D6C6F5C}"/>
 </file>
--- a/docs/commercial/tenders/sky-blog-2026/propuesta-economica.xlsx
+++ b/docs/commercial/tenders/sky-blog-2026/propuesta-economica.xlsx
@@ -6,12 +6,15 @@
   <sheets>
     <sheet sheetId="1" name="Propuesta Económica" state="visible" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Propuesta Económica'!$A1:$D45</definedName>
+  </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
   <si>
     <t>PROPUESTA ECONÓMICA</t>
   </si>
@@ -52,7 +55,7 @@
     <t>Alcance de la operación mensual</t>
   </si>
   <si>
-    <t>Valor mensual (CLP, neto sin IVA)</t>
+    <t>Valor mensual (neto, sin IVA)</t>
   </si>
   <si>
     <t>Plan propuesto</t>
@@ -76,13 +79,28 @@
     <t>Incluido</t>
   </si>
   <si>
-    <t>Proyección del plan propuesto</t>
+    <t>DETALLE DEL VALOR MENSUAL — PLAN PROPUESTO</t>
+  </si>
+  <si>
+    <t>Valor mensual neto</t>
+  </si>
+  <si>
+    <t>IVA (19%)</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>PROYECCIÓN DEL PLAN PROPUESTO</t>
   </si>
   <si>
     <t>Anual (12 meses)</t>
   </si>
   <si>
-    <t>Total contrato (24 meses)</t>
+    <t/>
+  </si>
+  <si>
+    <t>Total del contrato (24 meses)</t>
   </si>
   <si>
     <t>2. CONDICIONES COMERCIALES</t>
@@ -148,7 +166,7 @@
     <t>Las comisiones de Wherex aplicables al adjudicado son asumidas por Efeonce y están consideradas en esta oferta</t>
   </si>
   <si>
-    <t>Efeonce Group SpA — Empower your Growth</t>
+    <t>Documento integrante de la oferta económica. Valores expresados en pesos chilenos (CLP), netos sin IVA. El conteo de artículos es un techo de capacidad mensual, no una unidad de precio.</t>
   </si>
 </sst>
 </file>
@@ -156,9 +174,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="164" formatCode="$#,##0;[Red]-$#,##0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -168,56 +186,74 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF0F2A4A"/>
-      <sz val="16"/>
-      <name val="Calibri"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="15"/>
+      <name val="Aptos"/>
     </font>
     <font>
       <color rgb="FF5B6470"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <name val="Aptos"/>
     </font>
     <font>
       <b/>
+      <color rgb="FF00345F"/>
+      <sz val="10"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
       <color rgb="FF141821"/>
+      <sz val="10"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF00345F"/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
     </font>
     <font>
       <color rgb="FF141821"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0F2A4A"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
+      <sz val="9.5"/>
+      <name val="Aptos"/>
     </font>
     <font>
       <b/>
       <color rgb="FF141821"/>
       <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF141821"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <color rgb="FF00345F"/>
       <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0F2A4A"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <i/>
       <color rgb="FF5B6470"/>
       <sz val="10"/>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF5B6470"/>
+      <sz val="8.5"/>
+      <name val="Aptos"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -226,16 +262,40 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5F7FA"/>
+        <fgColor rgb="FF00345F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF36C8BF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFCFD"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF36C8BF"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -257,11 +317,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -271,45 +333,67 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -327,6 +411,50 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>44999</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>110000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1600200" cy="371475"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -651,230 +779,337 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C31"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="72" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="1" max="1" width="2.5" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="66" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" ht="3" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C9" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C10" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="D10" s="6"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C11" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="D11" s="6"/>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B13" s="7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="C15" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="D15" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" ht="76" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+    <row r="16" ht="74" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B16" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="C16" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="10">
+      <c r="D16" s="12">
         <v>5200000</v>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+    <row r="17" ht="48" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="C17" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="11">
+      <c r="D17" s="15">
         <v>6900000</v>
       </c>
     </row>
-    <row r="13" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+    <row r="18" ht="74" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B18" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="C18" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="D18" s="17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+    <row r="20" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B22" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="11">
+      <c r="C22" s="18"/>
+      <c r="D22" s="19">
+        <v>5200000</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B23" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="18"/>
+      <c r="D23" s="19">
+        <v>988000</v>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B24" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="20"/>
+      <c r="D24" s="21">
+        <v>6188000</v>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B26" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+    </row>
+    <row r="28" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B28" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="23">
         <v>62400000</v>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="17"/>
-      <c r="C17" s="18">
+    <row r="29" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B29" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="26">
         <v>124800000</v>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="16"/>
-    </row>
-    <row r="21" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="16"/>
-    </row>
-    <row r="22" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
+    <row r="31" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+    </row>
+    <row r="33" ht="32" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="16"/>
-    </row>
-    <row r="23" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
+      <c r="C33" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="D33" s="11"/>
+    </row>
+    <row r="34" ht="32" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="16"/>
-    </row>
-    <row r="24" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
+      <c r="C34" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="D34" s="14"/>
+    </row>
+    <row r="35" ht="32" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="16"/>
-    </row>
-    <row r="25" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+      <c r="C35" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="D35" s="11"/>
+    </row>
+    <row r="36" ht="32" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="C25" s="16"/>
-    </row>
-    <row r="26" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+      <c r="C36" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="D36" s="14"/>
+    </row>
+    <row r="37" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B37" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="16"/>
-    </row>
-    <row r="27" ht="46" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
+      <c r="C37" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="D37" s="11"/>
+    </row>
+    <row r="38" ht="32" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B38" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="16"/>
-    </row>
-    <row r="28" ht="46" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
+      <c r="C38" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="D38" s="14"/>
+    </row>
+    <row r="39" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B39" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="16"/>
-    </row>
-    <row r="29" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
+      <c r="C39" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="D39" s="11"/>
+    </row>
+    <row r="40" ht="46" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B40" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="16"/>
-    </row>
-    <row r="31" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
+      <c r="C40" s="14" t="s">
         <v>45</v>
       </c>
+      <c r="D40" s="14"/>
+    </row>
+    <row r="41" ht="46" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B41" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D41" s="11"/>
+    </row>
+    <row r="42" ht="32" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B42" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" s="14"/>
+    </row>
+    <row r="45" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B45" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C45" s="27"/>
+      <c r="D45" s="27"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <mergeCells count="24">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="B45:D45"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.6" header="0.2" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8&amp;K5B6470Efeonce Group SpA · Confidencial&amp;C&amp;8&amp;K5B6470Servicio de Producción de Contenido Blog — SKY Airline&amp;R&amp;8&amp;K5B6470Página &amp;P de &amp;N</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/commercial/tenders/sky-blog-2026/propuesta-economica.xlsx
+++ b/docs/commercial/tenders/sky-blog-2026/propuesta-economica.xlsx
@@ -6,12 +6,15 @@
   <sheets>
     <sheet sheetId="1" name="Propuesta Económica" state="visible" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Propuesta Económica'!$A1:$D45</definedName>
+  </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
   <si>
     <t>PROPUESTA ECONÓMICA</t>
   </si>
@@ -43,52 +46,70 @@
     <t>120 días desde su recepción por parte de SKY</t>
   </si>
   <si>
-    <t>1. TARIFAS</t>
+    <t>1. VALOR DEL SERVICIO</t>
   </si>
   <si>
     <t>Plan</t>
   </si>
   <si>
-    <t>Alcance mensual</t>
-  </si>
-  <si>
-    <t>Valor mensual (CLP, neto sin IVA)</t>
-  </si>
-  <si>
-    <t>Base (propuesto)</t>
-  </si>
-  <si>
-    <t>8 artículos/mes + SEO/AEO + recursos visuales + reportería</t>
-  </si>
-  <si>
-    <t>Ampliado (opcional)</t>
-  </si>
-  <si>
-    <t>12 artículos/mes + SEO/AEO + recursos visuales + reportería</t>
-  </si>
-  <si>
-    <t>Artículo adicional / ad-hoc</t>
-  </si>
-  <si>
-    <t>Por artículo, sobre el plan contratado</t>
-  </si>
-  <si>
-    <t>Valor del plan base — proyección del contrato</t>
+    <t>Alcance de la operación mensual</t>
+  </si>
+  <si>
+    <t>Valor mensual (neto, sin IVA)</t>
+  </si>
+  <si>
+    <t>Plan propuesto</t>
+  </si>
+  <si>
+    <t>Operación mensual del blog: estrategia y planificación editorial · capa técnica de SEO implementada sobre su WordPress · producción de hasta 8 artículos publicados · recursos visuales y multimedia · medición en buscadores y en los 5 motores de respuesta con IA · informe mensual con los 8 indicadores exigidos · portal de cliente en vivo · gobernanza con los 9 SLA de las Bases</t>
+  </si>
+  <si>
+    <t>Plan ampliado (opcional)</t>
+  </si>
+  <si>
+    <t>La misma operación, con capacidad de producción de hasta 12 artículos publicados al mes</t>
+  </si>
+  <si>
+    <t>Contenidos ad-hoc</t>
+  </si>
+  <si>
+    <t>Se producen DENTRO de la capacidad mensual contratada, con la prioridad que SKY determine y en ≤ 5 días hábiles. Sin costo adicional: un contenido ad-hoc ocupa un espacio de la capacidad del mes.</t>
+  </si>
+  <si>
+    <t>Incluido</t>
+  </si>
+  <si>
+    <t>DETALLE DEL VALOR MENSUAL — PLAN PROPUESTO</t>
+  </si>
+  <si>
+    <t>Valor mensual neto</t>
+  </si>
+  <si>
+    <t>IVA (19%)</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>PROYECCIÓN DEL PLAN PROPUESTO</t>
   </si>
   <si>
     <t>Anual (12 meses)</t>
   </si>
   <si>
-    <t>Total contrato (24 meses)</t>
+    <t/>
+  </si>
+  <si>
+    <t>Total del contrato (24 meses)</t>
   </si>
   <si>
     <t>2. CONDICIONES COMERCIALES</t>
   </si>
   <si>
-    <t>Moneda</t>
-  </si>
-  <si>
-    <t>Pesos chilenos (CLP) — proveedor chileno</t>
+    <t>Precio</t>
+  </si>
+  <si>
+    <t>CLP 5.200.000 mensuales, valor neto. Tarifa fija en pesos chilenos, conforme al numeral 3.2 de las Bases</t>
   </si>
   <si>
     <t>Impuestos</t>
@@ -100,43 +121,43 @@
     <t>Reajustes</t>
   </si>
   <si>
-    <t>Sin reajuste durante la vigencia del contrato</t>
+    <t>Sin reajuste durante la vigencia del contrato, conforme al numeral 3.2 de las Bases</t>
+  </si>
+  <si>
+    <t>Condiciones de pago</t>
+  </si>
+  <si>
+    <t>30 días desde la correcta recepción y aceptación conforme de la factura por parte de SKY</t>
+  </si>
+  <si>
+    <t>Facturación</t>
+  </si>
+  <si>
+    <t>Mensual</t>
+  </si>
+  <si>
+    <t>Modalidad de pago</t>
+  </si>
+  <si>
+    <t>Transferencia electrónica a la cuenta bancaria de Efeonce Group SpA</t>
+  </si>
+  <si>
+    <t>Duración</t>
+  </si>
+  <si>
+    <t>Dos (2) años a contar del inicio del servicio</t>
+  </si>
+  <si>
+    <t>Condiciones de término</t>
+  </si>
+  <si>
+    <t>Renovable por igual período previo acuerdo de ambas partes, con notificación 60 días antes del término del período en curso (numeral 3.3.2 de las Bases)</t>
   </si>
   <si>
     <t>Desembolsos</t>
   </si>
   <si>
-    <t>No aplican. El valor mensual es todo incluido (planificación, producción, SEO/AEO, recursos visuales, reportería y coordinación). Sin gastos reembolsables ni costos ocultos</t>
-  </si>
-  <si>
-    <t>Condiciones de pago</t>
-  </si>
-  <si>
-    <t>30 días desde la correcta recepción y aceptación conforme de la factura por parte de SKY</t>
-  </si>
-  <si>
-    <t>Facturación</t>
-  </si>
-  <si>
-    <t>Mensual</t>
-  </si>
-  <si>
-    <t>Modalidad de pago</t>
-  </si>
-  <si>
-    <t>Transferencia electrónica</t>
-  </si>
-  <si>
-    <t>Duración del contrato</t>
-  </si>
-  <si>
-    <t>Dos (2) años a contar del inicio del servicio</t>
-  </si>
-  <si>
-    <t>Condiciones de término</t>
-  </si>
-  <si>
-    <t>Renovable por igual período previo acuerdo de las partes, con aviso de 60 días antes del término</t>
+    <t>No aplican. El valor mensual es todo incluido: planificación, capa técnica, producción, recursos visuales, multimedia, medición, portal y coordinación. Sin gastos reembolsables ni costos ocultos</t>
   </si>
   <si>
     <t>Comisiones de plataforma</t>
@@ -145,14 +166,17 @@
     <t>Las comisiones de Wherex aplicables al adjudicado son asumidas por Efeonce y están consideradas en esta oferta</t>
   </si>
   <si>
-    <t>Efeonce Group SpA — Empower your Growth</t>
+    <t>Documento integrante de la oferta económica. Valores expresados en pesos chilenos (CLP), netos sin IVA. El conteo de artículos es un techo de capacidad mensual, no una unidad de precio.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="11" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0;[Red]-$#,##0"/>
+  </numFmts>
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -162,64 +186,74 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF023C70"/>
-      <sz val="18"/>
-      <name val="Calibri"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="15"/>
+      <name val="Aptos"/>
     </font>
     <font>
       <color rgb="FF5B6470"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF00345F"/>
+      <sz val="10"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <color rgb="FF141821"/>
+      <sz val="10"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF00345F"/>
+      <sz val="11"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <color rgb="FF141821"/>
+      <sz val="9.5"/>
+      <name val="Aptos"/>
     </font>
     <font>
       <b/>
       <color rgb="FF141821"/>
       <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF141821"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <color rgb="FF00345F"/>
       <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF023C70"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF5B6470"/>
+      <sz val="10"/>
+      <name val="Aptos"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <name val="Aptos"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF023C70"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF5B6470"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF023C70"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+      <name val="Aptos"/>
     </font>
     <font>
       <i/>
       <color rgb="FF5B6470"/>
-      <sz val="9"/>
-      <name val="Calibri"/>
+      <sz val="8.5"/>
+      <name val="Aptos"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -228,21 +262,40 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5F7FA"/>
+        <fgColor rgb="FF00345F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF023C70"/>
+        <fgColor rgb="FF36C8BF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFCFD"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF36C8BF"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -264,46 +317,84 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -320,6 +411,50 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>44999</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>110000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1600200" cy="371475"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -647,524 +782,334 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:D33"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="46" customWidth="1"/>
+    <col min="1" max="1" width="2.5" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="66" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+    <row r="1" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" ht="3" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="5" ht="16" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" ht="16" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C9" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" ht="16" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" ht="16" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
+      <c r="D10" s="6"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
+      <c r="D11" s="6"/>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B13" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" ht="30" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C15" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D15" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
+    <row r="16" ht="74" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B16" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C16" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D16" s="12">
         <v>5200000</v>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="4" t="s">
+    <row r="17" ht="48" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C17" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D17" s="15">
         <v>6900000</v>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
+    <row r="18" ht="74" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B18" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C18" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="10">
-        <v>260000</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="11" t="s">
+      <c r="D18" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-    </row>
-    <row r="17" ht="16" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="4" t="s">
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="12">
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B22" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="D22" s="19">
+        <v>5200000</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B23" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="18"/>
+      <c r="D23" s="19">
+        <v>988000</v>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B24" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="20"/>
+      <c r="D24" s="21">
+        <v>6188000</v>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B26" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+    </row>
+    <row r="28" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B28" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="23">
         <v>62400000</v>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="12">
+    <row r="29" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B29" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="26">
         <v>124800000</v>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="4"/>
-    </row>
-    <row r="23" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="4" t="s">
+    <row r="31" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24" ht="42" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="s">
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+    </row>
+    <row r="33" ht="32" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C33" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="4"/>
-    </row>
-    <row r="25" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="3" t="s">
+      <c r="D33" s="11"/>
+    </row>
+    <row r="34" ht="32" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C34" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="4"/>
-    </row>
-    <row r="26" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="3" t="s">
+      <c r="D34" s="14"/>
+    </row>
+    <row r="35" ht="32" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C35" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="4"/>
-    </row>
-    <row r="27" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B27" s="3" t="s">
+      <c r="D35" s="11"/>
+    </row>
+    <row r="36" ht="32" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C36" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B28" s="3" t="s">
+      <c r="D36" s="14"/>
+    </row>
+    <row r="37" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B37" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C37" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="4"/>
-    </row>
-    <row r="29" ht="42" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B29" s="3" t="s">
+      <c r="D37" s="11"/>
+    </row>
+    <row r="38" ht="32" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B38" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C38" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="4"/>
-    </row>
-    <row r="30" ht="42" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" s="3" t="s">
+      <c r="D38" s="14"/>
+    </row>
+    <row r="39" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B39" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C39" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D30" s="4"/>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B33" s="13" t="s">
+      <c r="D39" s="11"/>
+    </row>
+    <row r="40" ht="46" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B40" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
+      <c r="C40" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" s="14"/>
+    </row>
+    <row r="41" ht="46" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B41" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D41" s="11"/>
+    </row>
+    <row r="42" ht="32" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B42" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" s="14"/>
+    </row>
+    <row r="45" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B45" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C45" s="27"/>
+      <c r="D45" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="24">
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="B13:D13"/>
     <mergeCell ref="B20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="B45:D45"/>
   </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.6" header="0.2" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8&amp;K5B6470Efeonce Group SpA · Confidencial&amp;C&amp;8&amp;K5B6470Servicio de Producción de Contenido Blog — SKY Airline&amp;R&amp;8&amp;K5B6470Página &amp;P de &amp;N</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009D828160AC62D2469F2CE6ED288EED23" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="2cd7cb4357131406ef2560062547c01c">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89d25d81-5310-4cf1-bb5a-6a617d2b6a73" xmlns:ns3="3c9eec10-562a-438c-b6b5-17a823518688" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="93f478c6cac0bb3a9ff43bd8511d61be" ns2:_="" ns3:_="">
-    <xsd:import namespace="89d25d81-5310-4cf1-bb5a-6a617d2b6a73"/>
-    <xsd:import namespace="3c9eec10-562a-438c-b6b5-17a823518688"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:Fecha" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="89d25d81-5310-4cf1-bb5a-6a617d2b6a73" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="9" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="8b9bf029-62f4-4345-b8e5-422487cfd5ed" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="15" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Fecha" ma:index="19" nillable="true" ma:displayName="Fecha" ma:default="[today]" ma:format="DateTime" ma:internalName="Fecha">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:DateTime"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="22" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3c9eec10-562a-438c-b6b5-17a823518688" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="10" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{0ab32602-a2c3-4267-9b10-aa875bd30e36}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3c9eec10-562a-438c-b6b5-17a823518688">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="89d25d81-5310-4cf1-bb5a-6a617d2b6a73">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3c9eec10-562a-438c-b6b5-17a823518688" xsi:nil="true"/>
-    <Fecha xmlns="89d25d81-5310-4cf1-bb5a-6a617d2b6a73">2026-07-12T09:55:42+00:00</Fecha>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0FC00D0-9E4D-4F97-AAFC-33A791EFC979}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4994FC4-F8AC-4A2A-A98A-C829B40B4951}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01CFE923-56D7-42A4-A493-C93B7D6C6F5C}"/>
 </file>